--- a/data.mn/public/datasets/mongolbank-deposit-rate-mnt-monthly.xlsx
+++ b/data.mn/public/datasets/mongolbank-deposit-rate-mnt-monthly.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EN" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MN" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="EN" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="MN" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,6 +416,28 @@
   </sheetPr>
   <dimension ref="A1:T13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="14" max="14"/>
+    <col width="6" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="7" customWidth="1" min="17" max="17"/>
+    <col width="7" customWidth="1" min="18" max="18"/>
+    <col width="7" customWidth="1" min="19" max="19"/>
+    <col width="7" customWidth="1" min="20" max="20"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -485,9 +507,6 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>10.74</v>
       </c>
@@ -541,9 +560,6 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
         <v>10.6</v>
       </c>
@@ -589,13 +605,14 @@
       <c r="S3" t="n">
         <v>11.83</v>
       </c>
-      <c r="T3" t="inlineStr"/>
+      <c r="T3" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
         <v>13.5</v>
       </c>
@@ -647,15 +664,14 @@
       <c r="S4" t="n">
         <v>11.82</v>
       </c>
-      <c r="T4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>12.03</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
         <v>10.65</v>
       </c>
@@ -701,15 +717,14 @@
       <c r="S5" t="n">
         <v>11.84</v>
       </c>
-      <c r="T5" t="inlineStr"/>
+      <c r="T5" t="n">
+        <v>12.03</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
         <v>10.45</v>
       </c>
@@ -755,13 +770,14 @@
       <c r="S6" t="n">
         <v>11.83</v>
       </c>
-      <c r="T6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>12.04</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
         <v>13.17</v>
       </c>
@@ -813,15 +829,14 @@
       <c r="S7" t="n">
         <v>11.79</v>
       </c>
-      <c r="T7" t="inlineStr"/>
+      <c r="T7" t="n">
+        <v>11.95</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
         <v>10.4</v>
       </c>
@@ -867,15 +882,14 @@
       <c r="S8" t="n">
         <v>11.78</v>
       </c>
-      <c r="T8" t="inlineStr"/>
+      <c r="T8" t="n">
+        <v>11.97</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
         <v>10.35</v>
       </c>
@@ -921,13 +935,11 @@
       <c r="S9" t="n">
         <v>11.87</v>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
         <v>13.2</v>
       </c>
@@ -979,15 +991,11 @@
       <c r="S10" t="n">
         <v>11.86</v>
       </c>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
         <v>10.39</v>
       </c>
@@ -1033,15 +1041,11 @@
       <c r="S11" t="n">
         <v>11.89</v>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
         <v>10.5</v>
       </c>
@@ -1087,7 +1091,6 @@
       <c r="S12" t="n">
         <v>11.92</v>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1147,7 +1150,6 @@
       <c r="S13" t="n">
         <v>11.89</v>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1162,6 +1164,28 @@
   </sheetPr>
   <dimension ref="A1:T13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="14" max="14"/>
+    <col width="6" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="7" customWidth="1" min="17" max="17"/>
+    <col width="7" customWidth="1" min="18" max="18"/>
+    <col width="7" customWidth="1" min="19" max="19"/>
+    <col width="7" customWidth="1" min="20" max="20"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1231,9 +1255,6 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>10.74</v>
       </c>
@@ -1287,9 +1308,6 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
         <v>10.6</v>
       </c>
@@ -1335,13 +1353,14 @@
       <c r="S3" t="n">
         <v>11.83</v>
       </c>
-      <c r="T3" t="inlineStr"/>
+      <c r="T3" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
         <v>13.5</v>
       </c>
@@ -1393,15 +1412,14 @@
       <c r="S4" t="n">
         <v>11.82</v>
       </c>
-      <c r="T4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>12.03</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
         <v>10.65</v>
       </c>
@@ -1447,15 +1465,14 @@
       <c r="S5" t="n">
         <v>11.84</v>
       </c>
-      <c r="T5" t="inlineStr"/>
+      <c r="T5" t="n">
+        <v>12.03</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
         <v>10.45</v>
       </c>
@@ -1501,13 +1518,14 @@
       <c r="S6" t="n">
         <v>11.83</v>
       </c>
-      <c r="T6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>12.04</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
         <v>13.17</v>
       </c>
@@ -1559,15 +1577,14 @@
       <c r="S7" t="n">
         <v>11.79</v>
       </c>
-      <c r="T7" t="inlineStr"/>
+      <c r="T7" t="n">
+        <v>11.95</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
         <v>10.4</v>
       </c>
@@ -1613,15 +1630,14 @@
       <c r="S8" t="n">
         <v>11.78</v>
       </c>
-      <c r="T8" t="inlineStr"/>
+      <c r="T8" t="n">
+        <v>11.97</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
         <v>10.35</v>
       </c>
@@ -1667,13 +1683,11 @@
       <c r="S9" t="n">
         <v>11.87</v>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
         <v>13.2</v>
       </c>
@@ -1725,15 +1739,11 @@
       <c r="S10" t="n">
         <v>11.86</v>
       </c>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
         <v>10.39</v>
       </c>
@@ -1779,15 +1789,11 @@
       <c r="S11" t="n">
         <v>11.89</v>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
         <v>10.5</v>
       </c>
@@ -1833,7 +1839,6 @@
       <c r="S12" t="n">
         <v>11.92</v>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1893,7 +1898,6 @@
       <c r="S13" t="n">
         <v>11.89</v>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
